--- a/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
+++ b/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>3.898328466426899e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42938710435653e-12</v>
+        <v>1.94916423321345e-12</v>
       </c>
       <c r="J3" t="n">
         <v>0.9310344827586207</v>
@@ -599,7 +599,7 @@
         <v>0.002426031006193731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002965149007570115</v>
+        <v>0.003308224099355088</v>
       </c>
       <c r="M3" t="n">
         <v>0.8766233766233766</v>
@@ -608,7 +608,7 @@
         <v>5.107588530568728e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>2.809173691812801e-13</v>
+        <v>3.830691397926546e-13</v>
       </c>
       <c r="P3" t="n">
         <v>0.9030100334448159</v>
@@ -617,7 +617,7 @@
         <v>3.257250881274176e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>3.582975969401594e-15</v>
+        <v>4.885876321911264e-15</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         <v>0.0003084783794065122</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004241577716839543</v>
+        <v>0.0004627175691097683</v>
       </c>
       <c r="J4" t="n">
         <v>0.8721704394141145</v>
@@ -666,7 +666,7 @@
         <v>1.257025172799433e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.609092300264589e-09</v>
+        <v>6.285125863997167e-09</v>
       </c>
       <c r="P4" t="n">
         <v>0.8612754766600921</v>
@@ -675,7 +675,7 @@
         <v>2.179894510951001e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>3.425548517208716e-06</v>
+        <v>4.671202523466431e-06</v>
       </c>
     </row>
     <row r="5">
@@ -706,7 +706,7 @@
         <v>0.3579737530505324</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3579737530505324</v>
+        <v>0.3835433068398561</v>
       </c>
       <c r="J5" t="n">
         <v>0.8272727272727273</v>
@@ -715,7 +715,7 @@
         <v>0.003975819319238917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004373401251162808</v>
+        <v>0.004969774149048646</v>
       </c>
       <c r="M5" t="n">
         <v>0.8272727272727273</v>
@@ -724,7 +724,7 @@
         <v>1.301241713644353e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>3.578414712521972e-06</v>
+        <v>4.879656426166325e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8272727272727273</v>
@@ -733,7 +733,7 @@
         <v>0.02645579193634775</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0323348568110917</v>
+        <v>0.03607607991320148</v>
       </c>
     </row>
     <row r="6">
@@ -806,7 +806,7 @@
         <v>1.079975599721546e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>2.375946319387402e-10</v>
+        <v>2.699938999303866e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9586206896551724</v>
@@ -815,7 +815,7 @@
         <v>2.821011611228471e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>1.034370924117106e-25</v>
+        <v>1.410505805614235e-25</v>
       </c>
       <c r="M7" t="n">
         <v>0.7220779220779221</v>
@@ -833,7 +833,7 @@
         <v>3.598229028257603e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>6.596753218472273e-07</v>
+        <v>8.995572570644009e-07</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>2.546798861027892e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.002112495900973e-05</v>
+        <v>4.24466476837982e-05</v>
       </c>
       <c r="J8" t="n">
         <v>0.9481481481481482</v>
@@ -873,7 +873,7 @@
         <v>1.031350757150745e-21</v>
       </c>
       <c r="L8" t="n">
-        <v>2.836214582164548e-21</v>
+        <v>3.867565339315292e-21</v>
       </c>
       <c r="M8" t="n">
         <v>0.6649350649350649</v>
@@ -882,7 +882,7 @@
         <v>0.005486386845873307</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006035025530460638</v>
+        <v>0.006857983557341634</v>
       </c>
       <c r="P8" t="n">
         <v>0.7816793893129771</v>
@@ -891,7 +891,7 @@
         <v>0.02379423160546088</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0323348568110917</v>
+        <v>0.03569134740819132</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>1.311124176059161e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>3.605591484162692e-12</v>
+        <v>4.916715660221852e-12</v>
       </c>
       <c r="J9" t="n">
         <v>0.8707482993197279</v>
@@ -931,7 +931,7 @@
         <v>3.353311676371332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.37728568801693e-08</v>
+        <v>7.185667877938568e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.8311688311688312</v>
@@ -940,7 +940,7 @@
         <v>2.607868530396811e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>5.737310766872985e-06</v>
+        <v>7.823605591190435e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8504983388704319</v>
@@ -949,7 +949,7 @@
         <v>4.654750284911726e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.280056328350725e-12</v>
+        <v>1.745531356841897e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.2836634509190494</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3120297960109544</v>
+        <v>0.3273039818296724</v>
       </c>
       <c r="J11" t="n">
         <v>0.8979206049149339</v>
@@ -1031,7 +1031,7 @@
         <v>1.496555999356245e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>2.057764499114837e-06</v>
+        <v>2.244833999034367e-06</v>
       </c>
       <c r="M11" t="n">
         <v>0.6168831168831169</v>
@@ -1040,7 +1040,7 @@
         <v>0.004557602324553063</v>
       </c>
       <c r="O11" t="n">
-        <v>0.005570402841120411</v>
+        <v>0.006214912260754177</v>
       </c>
       <c r="P11" t="n">
         <v>0.731331793687452</v>
@@ -1049,7 +1049,7 @@
         <v>0.7285769687645042</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7285769687645041</v>
+        <v>0.7285769687645042</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>9.782979652529539e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>1.793546269630416e-09</v>
+        <v>2.096352782684901e-09</v>
       </c>
       <c r="J12" t="n">
         <v>0.6726190476190477</v>
@@ -1089,7 +1089,7 @@
         <v>3.471127295496704e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>6.363733375077291e-07</v>
+        <v>6.50836367905632e-07</v>
       </c>
       <c r="M12" t="n">
         <v>0.587012987012987</v>
@@ -1098,7 +1098,7 @@
         <v>5.5327352635804e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0001014334798323073</v>
+        <v>0.0001185586127910086</v>
       </c>
       <c r="P12" t="n">
         <v>0.6269070735090153</v>
@@ -1107,7 +1107,7 @@
         <v>1.794543653490477e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>3.947996037679048e-10</v>
+        <v>5.383630960471431e-10</v>
       </c>
     </row>
     <row r="13">
@@ -1138,7 +1138,7 @@
         <v>0.2145668843589063</v>
       </c>
       <c r="I13" t="n">
-        <v>0.262248414216441</v>
+        <v>0.2735597858610984</v>
       </c>
       <c r="J13" t="n">
         <v>0.6869834710743802</v>
@@ -1147,7 +1147,7 @@
         <v>7.312656571833097e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.149131747002344e-06</v>
+        <v>1.218776095305516e-06</v>
       </c>
       <c r="M13" t="n">
         <v>0.8636363636363636</v>
@@ -1156,7 +1156,7 @@
         <v>8.146675026613834e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>8.961342529275216e-16</v>
+        <v>1.222001253992075e-15</v>
       </c>
       <c r="P13" t="n">
         <v>0.7652474108170311</v>
@@ -1165,7 +1165,7 @@
         <v>0.07552880046449245</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0830816805109417</v>
+        <v>0.09441100058061556</v>
       </c>
     </row>
     <row r="14">
@@ -1196,7 +1196,7 @@
         <v>1.222307606494889e-31</v>
       </c>
       <c r="I14" t="n">
-        <v>6.72269183572189e-31</v>
+        <v>9.167307048711667e-31</v>
       </c>
       <c r="J14" t="n">
         <v>0.5862068965517241</v>
@@ -1205,7 +1205,7 @@
         <v>8.808479846134314e-41</v>
       </c>
       <c r="L14" t="n">
-        <v>4.844663915373872e-40</v>
+        <v>6.606359884600735e-40</v>
       </c>
       <c r="M14" t="n">
         <v>0.7948051948051948</v>
@@ -1214,7 +1214,7 @@
         <v>0.001273631959676603</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00175124394455533</v>
+        <v>0.002122719932794339</v>
       </c>
       <c r="P14" t="n">
         <v>0.6747519294377067</v>
@@ -1223,7 +1223,7 @@
         <v>2.029229487650119e-14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.440508121383772e-14</v>
+        <v>1.01461474382506e-13</v>
       </c>
     </row>
     <row r="15">
@@ -1254,7 +1254,7 @@
         <v>2.476354404093151e-34</v>
       </c>
       <c r="I15" t="n">
-        <v>2.723989844502467e-33</v>
+        <v>3.714531606139727e-33</v>
       </c>
       <c r="J15" t="n">
         <v>0.5774647887323944</v>
@@ -1263,7 +1263,7 @@
         <v>5.42006990924959e-43</v>
       </c>
       <c r="L15" t="n">
-        <v>5.962076900174549e-42</v>
+        <v>8.130104863874384e-42</v>
       </c>
       <c r="M15" t="n">
         <v>0.7987012987012987</v>
@@ -1272,7 +1272,7 @@
         <v>0.0006473807193389553</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001017312558961215</v>
+        <v>0.001213838848760541</v>
       </c>
       <c r="P15" t="n">
         <v>0.6702997275204359</v>
@@ -1281,7 +1281,239 @@
         <v>2.266982110996192e-15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.246840161047905e-14</v>
+        <v>1.700236583247144e-14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>579</v>
+      </c>
+      <c r="D16" t="n">
+        <v>923</v>
+      </c>
+      <c r="E16" t="n">
+        <v>227</v>
+      </c>
+      <c r="F16" t="n">
+        <v>191</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7822916666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2188478286888787</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2735597858610984</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7183622828784119</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.07323164084108497</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.08449804712432882</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7519480519480519</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3826081690642374</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4099373239973972</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.7347715736040609</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5385630220467568</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5770318093358108</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>594</v>
+      </c>
+      <c r="D17" t="n">
+        <v>940</v>
+      </c>
+      <c r="E17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F17" t="n">
+        <v>176</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7989583333333333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7388059701492538</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.3792691777623545</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4063598333168083</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.07689028424872894</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.08871955874853341</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7547649301143583</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5330064915987247</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5770318093358108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B BM25 RAG</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>585</v>
+      </c>
+      <c r="D18" t="n">
+        <v>803</v>
+      </c>
+      <c r="E18" t="n">
+        <v>347</v>
+      </c>
+      <c r="F18" t="n">
+        <v>185</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7229166666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.685211464870993e-09</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.909771496633113e-09</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6276824034334764</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.270956543443846e-13</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.677391358609616e-13</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7597402597402597</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.001712038138346044</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.002568057207519066</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6874265569917744</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.002049470782181621</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.003842757716590539</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1920</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B Semantic RAG</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>609</v>
+      </c>
+      <c r="D19" t="n">
+        <v>762</v>
+      </c>
+      <c r="E19" t="n">
+        <v>388</v>
+      </c>
+      <c r="F19" t="n">
+        <v>161</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7140625</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.750348129151377e-11</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.325104438745413e-10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6108324974924775</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.373559206926997e-16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.912067762078099e-15</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7909090909090909</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.336778886499158e-06</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.084194721624789e-05</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6893039049235994</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.002875329900762836</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.004792216501271393</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
+++ b/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -806,7 +806,7 @@
         <v>1.079975599721546e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>2.699938999303866e-10</v>
+        <v>3.103052579550191e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9586206896551724</v>
@@ -940,7 +940,7 @@
         <v>2.607868530396811e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>7.823605591190435e-06</v>
+        <v>6.519671325992029e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8504983388704319</v>
@@ -1138,7 +1138,7 @@
         <v>0.2145668843589063</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2735597858610984</v>
+        <v>0.2925912059439631</v>
       </c>
       <c r="J13" t="n">
         <v>0.6869834710743802</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D14" t="n">
         <v>718</v>
@@ -1187,43 +1187,43 @@
         <v>432</v>
       </c>
       <c r="F14" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6927083333333334</v>
+        <v>0.6942708333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>1.222307606494889e-31</v>
+        <v>4.117577404502676e-31</v>
       </c>
       <c r="I14" t="n">
-        <v>9.167307048711667e-31</v>
+        <v>3.088183053377007e-30</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5873925501432665</v>
       </c>
       <c r="K14" t="n">
-        <v>8.808479846134314e-41</v>
+        <v>1.805211985835998e-40</v>
       </c>
       <c r="L14" t="n">
-        <v>6.606359884600735e-40</v>
+        <v>1.353908989376998e-39</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7948051948051948</v>
+        <v>0.7987012987012987</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001273631959676603</v>
+        <v>0.0006473807193389553</v>
       </c>
       <c r="O14" t="n">
-        <v>0.002122719932794339</v>
+        <v>0.001078967865564925</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6747519294377067</v>
+        <v>0.6769400110071547</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.029229487650119e-14</v>
+        <v>4.977043957117427e-14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.01461474382506e-13</v>
+        <v>2.488521978558714e-13</v>
       </c>
     </row>
     <row r="15">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D15" t="n">
         <v>700</v>
@@ -1245,43 +1245,43 @@
         <v>450</v>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6848958333333334</v>
+        <v>0.6859375</v>
       </c>
       <c r="H15" t="n">
-        <v>2.476354404093151e-34</v>
+        <v>5.731870431420374e-34</v>
       </c>
       <c r="I15" t="n">
-        <v>3.714531606139727e-33</v>
+        <v>8.597805647130561e-33</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5774647887323944</v>
+        <v>0.5782567947516402</v>
       </c>
       <c r="K15" t="n">
-        <v>5.42006990924959e-43</v>
+        <v>6.351771824742588e-43</v>
       </c>
       <c r="L15" t="n">
-        <v>8.130104863874384e-42</v>
+        <v>9.527657737113881e-42</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7987012987012987</v>
+        <v>0.8012987012987013</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0006473807193389553</v>
+        <v>0.0004036047523908493</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001213838848760541</v>
+        <v>0.0007567589107328425</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6702997275204359</v>
+        <v>0.6717474142623843</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.266982110996192e-15</v>
+        <v>4.181092880882774e-15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.700236583247144e-14</v>
+        <v>3.13581966066208e-14</v>
       </c>
     </row>
     <row r="16">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D16" t="n">
         <v>923</v>
@@ -1303,43 +1303,43 @@
         <v>227</v>
       </c>
       <c r="F16" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7822916666666667</v>
+        <v>0.7838541666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2188478286888787</v>
+        <v>0.2660897050964158</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2735597858610984</v>
+        <v>0.3273039818296724</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7183622828784119</v>
+        <v>0.7194066749072929</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07323164084108497</v>
+        <v>0.082911067584413</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08449804712432882</v>
+        <v>0.09566661644355347</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7519480519480519</v>
+        <v>0.7558441558441559</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3826081690642374</v>
+        <v>0.2935542241514899</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4099373239973972</v>
+        <v>0.3145223830194534</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7347715736040609</v>
+        <v>0.7371754274857504</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5385630220467568</v>
+        <v>0.6515684127871353</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5770318093358108</v>
+        <v>0.698109013700502</v>
       </c>
     </row>
     <row r="17">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D17" t="n">
         <v>940</v>
@@ -1361,43 +1361,43 @@
         <v>210</v>
       </c>
       <c r="F17" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7989583333333333</v>
+        <v>0.8005208333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.9357265476780989</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.9357265476780989</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7388059701492538</v>
+        <v>0.7397769516728625</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3792691777623545</v>
+        <v>0.4117694201795677</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4063598333168083</v>
+        <v>0.4411815216209654</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7753246753246753</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07689028424872894</v>
+        <v>0.05102860211043558</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08871955874853341</v>
+        <v>0.05887915628127183</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7547649301143583</v>
+        <v>0.7571337983512998</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5330064915987247</v>
+        <v>0.4293499140786398</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5770318093358108</v>
+        <v>0.4954037470138151</v>
       </c>
     </row>
     <row r="18">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D18" t="n">
         <v>803</v>
@@ -1419,43 +1419,43 @@
         <v>347</v>
       </c>
       <c r="F18" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7229166666666667</v>
+        <v>0.7239583333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>3.685211464870993e-09</v>
+        <v>5.682798536205383e-09</v>
       </c>
       <c r="I18" t="n">
-        <v>6.909771496633113e-09</v>
+        <v>1.065524725538509e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6276824034334764</v>
+        <v>0.6284796573875803</v>
       </c>
       <c r="K18" t="n">
-        <v>2.270956543443846e-13</v>
+        <v>3.314512315873406e-13</v>
       </c>
       <c r="L18" t="n">
-        <v>5.677391358609616e-13</v>
+        <v>8.286280789683516e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7597402597402597</v>
+        <v>0.7623376623376623</v>
       </c>
       <c r="N18" t="n">
-        <v>0.001712038138346044</v>
+        <v>0.001133194537790146</v>
       </c>
       <c r="O18" t="n">
-        <v>0.002568057207519066</v>
+        <v>0.001699791806685218</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6874265569917744</v>
+        <v>0.6889671361502347</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.002049470782181621</v>
+        <v>0.002661164794431916</v>
       </c>
       <c r="R18" t="n">
-        <v>0.003842757716590539</v>
+        <v>0.004989683989559842</v>
       </c>
     </row>
     <row r="19">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D19" t="n">
         <v>762</v>
@@ -1477,43 +1477,43 @@
         <v>388</v>
       </c>
       <c r="F19" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7140625</v>
+        <v>0.7151041666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>7.750348129151377e-11</v>
+        <v>1.241221031820076e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>2.325104438745413e-10</v>
+        <v>3.103052579550191e-10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6108324974924775</v>
+        <v>0.6116116116116116</v>
       </c>
       <c r="K19" t="n">
-        <v>6.373559206926997e-16</v>
+        <v>6.724207503444439e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>1.912067762078099e-15</v>
+        <v>2.017262251033332e-15</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7909090909090909</v>
+        <v>0.7935064935064935</v>
       </c>
       <c r="N19" t="n">
-        <v>4.336778886499158e-06</v>
+        <v>2.367284350056279e-06</v>
       </c>
       <c r="O19" t="n">
-        <v>1.084194721624789e-05</v>
+        <v>6.519671325992029e-06</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6893039049235994</v>
+        <v>0.6907857546636517</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.002875329900762836</v>
+        <v>0.003690056298801989</v>
       </c>
       <c r="R19" t="n">
-        <v>0.004792216501271393</v>
+        <v>0.006150093831336648</v>
       </c>
     </row>
   </sheetData>

--- a/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
+++ b/rag/eval/results_original120/evaluation_metrics_fisher_original120.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>3.898328466426899e-13</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94916423321345e-12</v>
+        <v>2.338997079856139e-12</v>
       </c>
       <c r="J3" t="n">
         <v>0.9310344827586207</v>
@@ -599,7 +599,7 @@
         <v>0.002426031006193731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003308224099355088</v>
+        <v>0.003234708008258308</v>
       </c>
       <c r="M3" t="n">
         <v>0.8766233766233766</v>
@@ -608,7 +608,7 @@
         <v>5.107588530568728e-14</v>
       </c>
       <c r="O3" t="n">
-        <v>3.830691397926546e-13</v>
+        <v>3.064553118341237e-13</v>
       </c>
       <c r="P3" t="n">
         <v>0.9030100334448159</v>
@@ -617,7 +617,7 @@
         <v>3.257250881274176e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>4.885876321911264e-15</v>
+        <v>3.908701057529011e-15</v>
       </c>
     </row>
     <row r="4">
@@ -666,7 +666,7 @@
         <v>1.257025172799433e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>6.285125863997167e-09</v>
+        <v>5.028100691197733e-09</v>
       </c>
       <c r="P4" t="n">
         <v>0.8612754766600921</v>
@@ -675,7 +675,7 @@
         <v>2.179894510951001e-06</v>
       </c>
       <c r="R4" t="n">
-        <v>4.671202523466431e-06</v>
+        <v>4.359789021902002e-06</v>
       </c>
     </row>
     <row r="5">
@@ -706,7 +706,7 @@
         <v>0.3579737530505324</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3835433068398561</v>
+        <v>0.3905168215096717</v>
       </c>
       <c r="J5" t="n">
         <v>0.8272727272727273</v>
@@ -715,7 +715,7 @@
         <v>0.003975819319238917</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004969774149048646</v>
+        <v>0.0047709831830867</v>
       </c>
       <c r="M5" t="n">
         <v>0.8272727272727273</v>
@@ -724,7 +724,7 @@
         <v>1.301241713644353e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>4.879656426166325e-06</v>
+        <v>3.90372514093306e-06</v>
       </c>
       <c r="P5" t="n">
         <v>0.8272727272727273</v>
@@ -733,7 +733,7 @@
         <v>0.02645579193634775</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03607607991320148</v>
+        <v>0.03527438924846367</v>
       </c>
     </row>
     <row r="6">
@@ -806,7 +806,7 @@
         <v>1.079975599721546e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>3.103052579550191e-10</v>
+        <v>2.978930476368183e-10</v>
       </c>
       <c r="J7" t="n">
         <v>0.9586206896551724</v>
@@ -815,7 +815,7 @@
         <v>2.821011611228471e-26</v>
       </c>
       <c r="L7" t="n">
-        <v>1.410505805614235e-25</v>
+        <v>1.692606966737083e-25</v>
       </c>
       <c r="M7" t="n">
         <v>0.7220779220779221</v>
@@ -833,7 +833,7 @@
         <v>3.598229028257603e-07</v>
       </c>
       <c r="R7" t="n">
-        <v>8.995572570644009e-07</v>
+        <v>8.635749667818249e-07</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +864,7 @@
         <v>2.546798861027892e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.24466476837982e-05</v>
+        <v>4.365940904619243e-05</v>
       </c>
       <c r="J8" t="n">
         <v>0.9481481481481482</v>
@@ -873,7 +873,7 @@
         <v>1.031350757150745e-21</v>
       </c>
       <c r="L8" t="n">
-        <v>3.867565339315292e-21</v>
+        <v>4.125403028602978e-21</v>
       </c>
       <c r="M8" t="n">
         <v>0.6649350649350649</v>
@@ -882,7 +882,7 @@
         <v>0.005486386845873307</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006857983557341634</v>
+        <v>0.006583664215047969</v>
       </c>
       <c r="P8" t="n">
         <v>0.7816793893129771</v>
@@ -891,7 +891,7 @@
         <v>0.02379423160546088</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03569134740819132</v>
+        <v>0.03527438924846367</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>1.311124176059161e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>4.916715660221852e-12</v>
+        <v>5.244496704236642e-12</v>
       </c>
       <c r="J9" t="n">
         <v>0.8707482993197279</v>
@@ -931,7 +931,7 @@
         <v>3.353311676371332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.185667877938568e-08</v>
+        <v>8.047948023291197e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.8311688311688312</v>
@@ -940,7 +940,7 @@
         <v>2.607868530396811e-06</v>
       </c>
       <c r="O9" t="n">
-        <v>6.519671325992029e-06</v>
+        <v>5.215737060793623e-06</v>
       </c>
       <c r="P9" t="n">
         <v>0.8504983388704319</v>
@@ -949,7 +949,7 @@
         <v>4.654750284911726e-13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.745531356841897e-12</v>
+        <v>1.861900113964691e-12</v>
       </c>
     </row>
     <row r="10">
@@ -1022,7 +1022,7 @@
         <v>0.2836634509190494</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3273039818296724</v>
+        <v>0.3403961411028593</v>
       </c>
       <c r="J11" t="n">
         <v>0.8979206049149339</v>
@@ -1040,7 +1040,7 @@
         <v>0.004557602324553063</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006214912260754177</v>
+        <v>0.006076803099404084</v>
       </c>
       <c r="P11" t="n">
         <v>0.731331793687452</v>
@@ -1080,7 +1080,7 @@
         <v>9.782979652529539e-10</v>
       </c>
       <c r="I12" t="n">
-        <v>2.096352782684901e-09</v>
+        <v>1.956595930505908e-09</v>
       </c>
       <c r="J12" t="n">
         <v>0.6726190476190477</v>
@@ -1089,7 +1089,7 @@
         <v>3.471127295496704e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>6.50836367905632e-07</v>
+        <v>6.942254590993407e-07</v>
       </c>
       <c r="M12" t="n">
         <v>0.587012987012987</v>
@@ -1098,7 +1098,7 @@
         <v>5.5327352635804e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0001185586127910086</v>
+        <v>9.484689023280686e-05</v>
       </c>
       <c r="P12" t="n">
         <v>0.6269070735090153</v>
@@ -1138,7 +1138,7 @@
         <v>0.2145668843589063</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2925912059439631</v>
+        <v>0.2860891791452083</v>
       </c>
       <c r="J13" t="n">
         <v>0.6869834710743802</v>
@@ -1147,7 +1147,7 @@
         <v>7.312656571833097e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.218776095305516e-06</v>
+        <v>1.253598269457102e-06</v>
       </c>
       <c r="M13" t="n">
         <v>0.8636363636363636</v>
@@ -1156,7 +1156,7 @@
         <v>8.146675026613834e-17</v>
       </c>
       <c r="O13" t="n">
-        <v>1.222001253992075e-15</v>
+        <v>9.776010031936602e-16</v>
       </c>
       <c r="P13" t="n">
         <v>0.7652474108170311</v>
@@ -1165,7 +1165,7 @@
         <v>0.07552880046449245</v>
       </c>
       <c r="R13" t="n">
-        <v>0.09441100058061556</v>
+        <v>0.09063456055739094</v>
       </c>
     </row>
     <row r="14">
@@ -1174,56 +1174,56 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-4o BM25 RAG</t>
+          <t>GPT-4o RAG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D14" t="n">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="E14" t="n">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="F14" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6942708333333333</v>
+        <v>0.6859375</v>
       </c>
       <c r="H14" t="n">
-        <v>4.117577404502676e-31</v>
+        <v>5.731870431420374e-34</v>
       </c>
       <c r="I14" t="n">
-        <v>3.088183053377007e-30</v>
+        <v>6.878244517704448e-33</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5873925501432665</v>
+        <v>0.5782567947516402</v>
       </c>
       <c r="K14" t="n">
-        <v>1.805211985835998e-40</v>
+        <v>6.351771824742588e-43</v>
       </c>
       <c r="L14" t="n">
-        <v>1.353908989376998e-39</v>
+        <v>7.622126189691105e-42</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7987012987012987</v>
+        <v>0.8012987012987013</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0006473807193389553</v>
+        <v>0.0004036047523908493</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001078967865564925</v>
+        <v>0.000605407128586274</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6769400110071547</v>
+        <v>0.6717474142623843</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.977043957117427e-14</v>
+        <v>4.181092880882774e-15</v>
       </c>
       <c r="R14" t="n">
-        <v>2.488521978558714e-13</v>
+        <v>2.508655728529664e-14</v>
       </c>
     </row>
     <row r="15">
@@ -1232,56 +1232,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4o Semantic RAG</t>
+          <t>Llama3.1-70B RAG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="D15" t="n">
-        <v>700</v>
+        <v>940</v>
       </c>
       <c r="E15" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6859375</v>
+        <v>0.8005208333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>5.731870431420374e-34</v>
+        <v>0.9357265476780989</v>
       </c>
       <c r="I15" t="n">
-        <v>8.597805647130561e-33</v>
+        <v>0.9357265476780988</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5782567947516402</v>
+        <v>0.7397769516728625</v>
       </c>
       <c r="K15" t="n">
-        <v>6.351771824742588e-43</v>
+        <v>0.4117694201795677</v>
       </c>
       <c r="L15" t="n">
-        <v>9.527657737113881e-42</v>
+        <v>0.4492030038322557</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8012987012987013</v>
+        <v>0.7753246753246753</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0004036047523908493</v>
+        <v>0.05102860211043558</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0007567589107328425</v>
+        <v>0.055667565938657</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6717474142623843</v>
+        <v>0.7571337983512998</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.181092880882774e-15</v>
+        <v>0.4293499140786398</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13581966066208e-14</v>
+        <v>0.4683817244494252</v>
       </c>
     </row>
     <row r="16">
@@ -1290,230 +1290,56 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Llama3.1-70B BM25 RAG</t>
+          <t>Llama3.1-8B RAG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="D16" t="n">
-        <v>923</v>
+        <v>762</v>
       </c>
       <c r="E16" t="n">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="F16" t="n">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7838541666666666</v>
+        <v>0.7151041666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2660897050964158</v>
+        <v>1.241221031820076e-10</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3273039818296724</v>
+        <v>2.978930476368183e-10</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7194066749072929</v>
+        <v>0.6116116116116116</v>
       </c>
       <c r="K16" t="n">
-        <v>0.082911067584413</v>
+        <v>6.724207503444439e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09566661644355347</v>
+        <v>2.017262251033332e-15</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7558441558441559</v>
+        <v>0.7935064935064935</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2935542241514899</v>
+        <v>2.367284350056279e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145223830194534</v>
+        <v>5.215737060793623e-06</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7371754274857504</v>
+        <v>0.6907857546636517</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6515684127871353</v>
+        <v>0.003690056298801989</v>
       </c>
       <c r="R16" t="n">
-        <v>0.698109013700502</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>597</v>
-      </c>
-      <c r="D17" t="n">
-        <v>940</v>
-      </c>
-      <c r="E17" t="n">
-        <v>210</v>
-      </c>
-      <c r="F17" t="n">
-        <v>173</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8005208333333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9357265476780989</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9357265476780989</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7397769516728625</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.4117694201795677</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.4411815216209654</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7753246753246753</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.05102860211043558</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.05887915628127183</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.7571337983512998</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.4293499140786398</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.4954037470138151</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B BM25 RAG</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>587</v>
-      </c>
-      <c r="D18" t="n">
-        <v>803</v>
-      </c>
-      <c r="E18" t="n">
-        <v>347</v>
-      </c>
-      <c r="F18" t="n">
-        <v>183</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.7239583333333334</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5.682798536205383e-09</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.065524725538509e-08</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6284796573875803</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.314512315873406e-13</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8.286280789683516e-13</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7623376623376623</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.001133194537790146</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.001699791806685218</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.6889671361502347</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.002661164794431916</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.004989683989559842</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1920</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B Semantic RAG</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>611</v>
-      </c>
-      <c r="D19" t="n">
-        <v>762</v>
-      </c>
-      <c r="E19" t="n">
-        <v>388</v>
-      </c>
-      <c r="F19" t="n">
-        <v>159</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.7151041666666667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.241221031820076e-10</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.103052579550191e-10</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6116116116116116</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.724207503444439e-16</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.017262251033332e-15</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.7935064935064935</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.367284350056279e-06</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6.519671325992029e-06</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.6907857546636517</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.003690056298801989</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.006150093831336648</v>
+        <v>0.006325810797946266</v>
       </c>
     </row>
   </sheetData>
